--- a/IT23600898_Test cases.xlsx
+++ b/IT23600898_Test cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IT23600898\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_4D59502E51298BE48711DBD36C31E1815659BF60" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC08674F-1F60-4025-98B9-7064A0D1FD5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="722" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="288">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -731,13 +731,277 @@
   </si>
   <si>
     <t>හෙට 9ඊයෙමට ක්ලෝමිට්ර්-5ක් පියාන් යමු.</t>
+  </si>
+  <si>
+    <t>Evidence or rationale for the input type covered</t>
+  </si>
+  <si>
+    <t>Rationale: The input represents a question structure in informal Singlish.
+Evidence: The sentence ends with “kamathida” which is a typical yes/no question indicator.</t>
+  </si>
+  <si>
+    <t>Rationale: The input is a past-tense question.
+Evidence: The phrase “ptan gattada?” indicates asking about a completed action.
+Rationale: It follows Sinhala interrogative structure.
+Evidence: The suffix “-da” marks the sentence as a question.</t>
+  </si>
+  <si>
+    <t>Rationale: Authority-based instruction is implied.
+Evidence: “guruthumiya kiuwa” shows the command comes from a teacher.
+Rationale: Sinhala directive structure is used.
+Evidence: Verb phrase “aran enna” reflects an action command.</t>
+  </si>
+  <si>
+    <t>Rationale: Future plan/decision is embedded.
+Evidence: “labana sathiye” indicates a planned future time.
+Rationale: Informal spoken style is used.
+Evidence: Words like “Thatta” and “kiyl” reflect casual usage.</t>
+  </si>
+  <si>
+    <t>Rationale: The sentence is a formal greeting/blessing.
+Evidence: “suba vesak mangalyk wewaa” is a traditional wish.</t>
+  </si>
+  <si>
+    <t>Rationale: The intended output is a blessing statement
+Evidence: “saukhya sampanna saha sarthaka
+ jeewithayak” expresses well-wishing.</t>
+  </si>
+  <si>
+    <t>Rationale: The sentence is a polite request.
+Evidence: “Oyta puluwnda” asks for permission/help.
+Rationale: Action request is clearly defined.
+Evidence: “gihin danna” indicates asking someone to drop off.</t>
+  </si>
+  <si>
+    <t>Rationale: Conditional polite request is present.
+Evidence: “puluwn nm” (if possible) softens the request.
+Rationale: Educational/information request.
+Evidence: “mahawnshya gana kiyl denna” asks for explanation.</t>
+  </si>
+  <si>
+    <t>Rationale: The sentence expresses gratitude.
+Evidence: “Godak stuti” directly means thank you.
+Rationale: It reflects a response after receiving help.
+Evidence: “alut dewal godak danagatta” shows gained knowledge.</t>
+  </si>
+  <si>
+    <t>Rationale: The sentence is a thankful response.
+Evidence: “stuti” indicates gratitude.</t>
+  </si>
+  <si>
+    <t>Rationale: The input contains repetition for emphasis.
+Evidence: The phrase “piywren piywr” repeats the same word pattern.
+Rationale: It follows formal Sinhala expression style.
+Evidence: “prayathnyn sarthkthwya” reflects structured wording.</t>
+  </si>
+  <si>
+    <t>Rationale: The sentence includes repetition to indicate gradual progression.
+Evidence: “kra krmyen” shows repeated structure meaning “step by step”.
+Rationale: Formal Sinhala grammar is used.
+Evidence: Words like “adyapnya karyehi” reflect formal usage.</t>
+  </si>
+  <si>
+    <t>Rationale: The sentence uses punctuation to separate clauses.
+Evidence: Commas in “Krunakrla , mehi ikmnin pamina” structure the sentence.
+Rationale: It is a formal request/instruction.
+Evidence: “katayuthu krnna” indicates an action directive.</t>
+  </si>
+  <si>
+    <t>Rationale: The sentence includes an exclamatory structure.
+Evidence: The “!” after “arumykd meh” indicates emphasis.
+Rationale: It expresses a strong reaction/opinion.
+Evidence: “kisisethma piligta nohaki” shows rejection.</t>
+  </si>
+  <si>
+    <t>Rationale: The input contains English words embedded in Singlish.
+Evidence: Words like “project”, “complete”, “try”.</t>
+  </si>
+  <si>
+    <t>Rationale: The sentence is fully in romanized Sinhala.
+Evidence: Words like “hithana widiyata”, “anivaryenma”.
+Rationale: It expresses certainty/necessity.
+Evidence: “anivaryenma sidu wenawa” indicates inevitability.</t>
+  </si>
+  <si>
+    <t>Rationale: Multiple English technical terms are embedded.
+Evidence: “release”, “camera quality”, “YouTube reviews”, “processor”.
+Rationale: Product discussion context is present.
+Evidence: Reference to “Samsung S24 Ultra”.
+Rationale: Informal conversational style is used.
+Evidence: Words like “Mcn”, “Mama baluwa”.</t>
+  </si>
+  <si>
+    <t>Rationale: The sentence mixes English technical/career terms.
+Evidence: “IT industry”, “internship”, “software engineering”, “data science”.
+Rationale: It expresses uncertainty about future decisions.
+Evidence: “hithaaganna ba” indicates confusion.
+Rationale: Informal spoken Sinhala is used.
+Evidence: “aney mndaa ban” shows casual tone.</t>
+  </si>
+  <si>
+    <t>Rationale: Multi-word English phrases are embedded.
+Evidence: “too much spicy”, “hard to eat”.</t>
+  </si>
+  <si>
+    <t>Rationale: The sentence contains multiple English phrases.
+Evidence: “work from home”, “technical support”, “waste of time”, “need a break”.
+Rationale: It expresses stress/frustration.
+Evidence: “feeling so stressed” directly states emotion.</t>
+  </si>
+  <si>
+    <t>Rationale: The input contains multiple English digital/payment-related terms.
+Evidence: “online card payment”, “transaction fail”, “customer care”, “message”.</t>
+  </si>
+  <si>
+    <t>Rationale: The input includes mobile/network-related digital terms.
+Evidence: “mobile data”, “recharge”, “server error”, “hotspot”, “connection”.
+Rationale: It expresses a technical problem scenario.
+Evidence: “data iwarai”, “server error enwa”.</t>
+  </si>
+  <si>
+    <t>Rationale: The input contains a social media platform name.
+Evidence: “Instagram”.</t>
+  </si>
+  <si>
+    <t>Rationale: Multiple platform/app names are used.
+Evidence: “Zoom”, “Telegram”.</t>
+  </si>
+  <si>
+    <t>Rationale: Multiple platform/app names are used.
+Evidence: “Zoom”, “Telegram”.
+Rationale: Digital communication context is present.
+Evidence: “group eka”, “message ekak”.</t>
+  </si>
+  <si>
+    <t>Rationale: The input includes multiple workplace abbreviations.
+Evidence: “CEO”, “ASAP”, “QA”, “WFH”, “VPN”.
+Rationale: Work/IT-related context is present.
+Evidence: “project eka QA karanna”, “VPN connection”.</t>
+  </si>
+  <si>
+    <t>Rationale: The input uses clipped English forms.
+Evidence: “egsameka” (exam).</t>
+  </si>
+  <si>
+    <t>Rationale: Multiple clipped/shortened English forms are used.
+Evidence: “lapripote” (lab report), “subit” (submit), “egsameka” (exam), “dout” (doubt).</t>
+  </si>
+  <si>
+    <t>Rationale: The input contains a place name.
+Evidence: “Singapore”.
+Rationale: Travel planning context is present.
+Evidence: “trip ekak ymuada”, “ticket price reduce wela”.</t>
+  </si>
+  <si>
+    <t>Rationale: The input includes a place name.
+Evidence: “NuwaraEliye”.</t>
+  </si>
+  <si>
+    <t>Rationale: The input contains a person’s name embedded in the sentence.
+Evidence: “Rashminiyi”.</t>
+  </si>
+  <si>
+    <t>Rationale: The input includes a person’s name.
+Evidence: “Rashminige”.
+Rationale: Social media/digital context is present.
+Evidence: “FB eke”, “issue ekak”.</t>
+  </si>
+  <si>
+    <t>Rationale: The input contains numbers combined with Sinhala suffixes.
+Evidence: “5denkma”, “100n100yama”.</t>
+  </si>
+  <si>
+    <t>Rationale: The input includes ordinal numbers and numeric forms.
+Evidence: “1st”, “2nd”, “3ne”, “5wa”.
+Rationale: Travel/plan context is present.
+Evidence: “trip-eke”, “travel krmu”.</t>
+  </si>
+  <si>
+    <t>Rationale: The input contains currency notation.
+Evidence: “Rs.5800k”.
+Rationale: Comparison context is present.
+Evidence: “Lastmnth ekat wada … double wela”.</t>
+  </si>
+  <si>
+    <t>Rationale: The input includes currency with numeric suffix.
+Evidence: “Rs9900k”.</t>
+  </si>
+  <si>
+    <t>Rationale: The input contains a time format.
+Evidence: “8:30AM”.
+Rationale: Scheduling/meeting context is present.
+Evidence: “meeting eka heta … patangnna”.</t>
+  </si>
+  <si>
+    <t>Rationale: The input includes time with PM format.
+Evidence: “7.45PM”.</t>
+  </si>
+  <si>
+    <t>Rationale: The input contains a standard date format.
+Evidence: “2026-02-06”.</t>
+  </si>
+  <si>
+    <t>Rationale: The input includes a natural language date.
+Evidence: “Februwari-15”.
+Rationale: Administrative/form context is present.
+Evidence: “Form eka bara denna”.</t>
+  </si>
+  <si>
+    <t>Rationale: The input contains a unit of measurement.
+Evidence: “klomitr-3k” (kilometers).
+Rationale: It describes physical movement/distance.
+Evidence: “piyn giya” indicates walking.</t>
+  </si>
+  <si>
+    <t>Rationale: The input includes a measurement unit.
+Evidence: “500gram”.</t>
+  </si>
+  <si>
+    <t>Rationale: The input contains Sinhala slang expressions.
+Evidence: “elakiry”, “mcn”, “umba”.</t>
+  </si>
+  <si>
+    <t>Rationale: The input includes slang and informal expressions.
+Evidence: “patta”, “elakiry”.
+Rationale: It expresses excitement or admiration.
+Evidence: “geyma gahuwa”.</t>
+  </si>
+  <si>
+    <t>Rationale: The input contains a website URL.
+Evidence: “www.webportl.lk”
+Rationale: Digital/web context is present.
+Evidence: “site-eka”, “details thiyenne”.</t>
+  </si>
+  <si>
+    <t>Rationale: The input includes a social media identifier.
+Evidence: “@chath_99_t”.</t>
+  </si>
+  <si>
+    <t>Rationale: The input contains an emoji.
+Evidence: “🤦‍♂️”.</t>
+  </si>
+  <si>
+    <t>Rationale: Multiple emojis are used.
+Evidence: “😫”, “😡”, “🙄🏃‍♂️”.
+Rationale: It expresses emotional state (stress/anger).
+Evidence: “wada-godat”, “balagidala”.</t>
+  </si>
+  <si>
+    <t>Rationale: The input combines multiple error types.
+Evidence: Person names (“Rashmini”), currency (“Rs.5000k”), mention (“@Tharindu_Ayya”).
+Rationale: It includes mixed English and Sinhala with slang.
+Evidence: “out-source”, “idea ekk”, “asap”.</t>
+  </si>
+  <si>
+    <t>Rationale: The input uses phonetic/encoded spelling.
+Evidence: “9eeyemt”, “klomitr”.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -748,6 +1012,18 @@
     <font>
       <b/>
       <sz val="8.5"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="8.5"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -788,10 +1064,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1073,7 +1358,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr defaultRowHeight="49.95" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.88671875" customWidth="1"/>
@@ -1082,12 +1367,12 @@
     <col min="4" max="4" width="22.109375" customWidth="1"/>
     <col min="5" max="5" width="25.33203125" customWidth="1"/>
     <col min="6" max="6" width="22.5546875" customWidth="1"/>
-    <col min="8" max="8" width="14.33203125" customWidth="1"/>
+    <col min="8" max="8" width="40.21875" customWidth="1"/>
     <col min="9" max="9" width="16" customWidth="1"/>
     <col min="10" max="11" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1109,1159 +1394,1311 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="G2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="114.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="G3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="118.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="G4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="109.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+      <c r="G5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="G6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="85.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="G7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="100.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="G8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="108.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+      <c r="G9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="114.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+      <c r="G10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="G11" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
+      <c r="G11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="127.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="G12" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+      <c r="G12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="G13" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
+      <c r="G13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="126" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="G14" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
+      <c r="G14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="108.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="G15" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
+      <c r="G15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="75.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="G16" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
+      <c r="G16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="104.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="G17" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="210" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
+      <c r="G17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="210" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="G18" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="226.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
+      <c r="G18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="175.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E19" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="G19" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
+      <c r="G19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E20" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="G20" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="173.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
+      <c r="G20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="173.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="G21" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="103.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
+      <c r="G21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="103.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F22" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="G22" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="85.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
+      <c r="G22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="123.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E23" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F23" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G23" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
+      <c r="G23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E24" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F24" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="G24" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
+      <c r="G24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E25" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="F25" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="G25" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="76.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
+      <c r="G25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="92.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E26" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="F26" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="G26" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="83.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
+      <c r="G26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="83.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="E27" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="F27" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="G27" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="76.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
+      <c r="G27" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="76.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="E28" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F28" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="G28" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
+      <c r="G28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D29" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E29" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F29" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="G29" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="64.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
+      <c r="G29" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="64.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="E30" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="F30" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="G30" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
+      <c r="G30" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D31" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="E31" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="F31" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="G31" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
+      <c r="G31" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="E32" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F32" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="G32" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
+      <c r="G32" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="91.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E33" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F33" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="G33" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
+      <c r="G33" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="74.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D34" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="E34" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="F34" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="G34" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
+      <c r="G34" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="109.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D35" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="E35" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="F35" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="G35" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="66" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
+      <c r="G35" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D36" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="E36" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="F36" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="G36" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
+      <c r="G36" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D37" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="E37" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="F37" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="G37" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="1" t="s">
+      <c r="G37" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="96.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D38" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="E38" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="F38" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="G38" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="1" t="s">
+      <c r="G38" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D39" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="E39" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="F39" s="1" t="s">
+      <c r="F39" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="G39" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="1" t="s">
+      <c r="G39" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D40" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="E40" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="F40" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="G40" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="1" t="s">
+      <c r="G40" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="103.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D41" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E41" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="F41" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="G41" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="1" t="s">
+      <c r="G41" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="98.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D42" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="E42" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="F42" s="1" t="s">
+      <c r="F42" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="G42" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="1" t="s">
+      <c r="G42" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D43" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="E43" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="F43" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="G43" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="1" t="s">
+      <c r="G43" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="68.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D44" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="E44" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="F44" s="1" t="s">
+      <c r="F44" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="G44" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="1" t="s">
+      <c r="G44" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="103.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B45" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D45" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="E45" s="1" t="s">
+      <c r="E45" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="F45" s="1" t="s">
+      <c r="F45" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="G45" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="1" t="s">
+      <c r="G45" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="105.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B46" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="D46" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E46" s="1" t="s">
+      <c r="E46" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="F46" s="1" t="s">
+      <c r="F46" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="G46" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="1" t="s">
+      <c r="G46" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D47" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="E47" s="1" t="s">
+      <c r="E47" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="F47" s="1" t="s">
+      <c r="F47" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="G47" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="1" t="s">
+      <c r="G47" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="67.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B48" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="D48" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="E48" s="1" t="s">
+      <c r="E48" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="F48" s="1" t="s">
+      <c r="F48" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="G48" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="1" t="s">
+      <c r="G48" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="108.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="D49" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="E49" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="F49" s="1" t="s">
+      <c r="F49" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="G49" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="1" t="s">
+      <c r="G49" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="129" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D50" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="E50" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="F50" s="1" t="s">
+      <c r="F50" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="G50" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="1" t="s">
+      <c r="G50" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B51" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C51" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="D51" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="E51" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="F51" s="1" t="s">
+      <c r="F51" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="G51" s="1" t="s">
-        <v>13</v>
+      <c r="G51" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>287</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>